--- a/InputData/trans/BRZSPbS/BAU Required ZEV Sales Perc by Subregion.xlsx
+++ b/InputData/trans/BRZSPbS/BAU Required ZEV Sales Perc by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\State Models\eps-maryland\InputData\trans\BRZSPbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A25693-6FEA-45BF-9AE8-0805CAC46FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBC4FF3-5DA9-4781-AF0A-8E522124D4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31845" yWindow="660" windowWidth="21825" windowHeight="15060" firstSheet="5" activeTab="8" xr2:uid="{8F1AFB95-7E48-4A2A-86D9-67ED7638AFF8}"/>
+    <workbookView xWindow="29235" yWindow="3030" windowWidth="17505" windowHeight="9735" firstSheet="2" activeTab="3" xr2:uid="{8F1AFB95-7E48-4A2A-86D9-67ED7638AFF8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -44,165 +44,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="194">
   <si>
     <t>BRZSPbS BAU Required ZEV Sales Percentage by Subregion</t>
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alaska </t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colorado </t>
-  </si>
-  <si>
-    <t>Connecticut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delaware </t>
-  </si>
-  <si>
-    <t>District of Columbia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florida </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgia </t>
-  </si>
-  <si>
-    <t>Hawaii</t>
-  </si>
-  <si>
-    <t>Idaho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illinois </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indiana </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iowa </t>
-  </si>
-  <si>
-    <t>Kansas</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maine </t>
-  </si>
-  <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minnesota </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mississippi </t>
-  </si>
-  <si>
-    <t>Missouri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montana </t>
-  </si>
-  <si>
-    <t>Nebraska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nevada </t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Jersey </t>
-  </si>
-  <si>
-    <t>New Mexico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New York </t>
-  </si>
-  <si>
-    <t>North Carolina</t>
-  </si>
-  <si>
-    <t>North Dakota</t>
-  </si>
-  <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oregon </t>
-  </si>
-  <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhode Island </t>
-  </si>
-  <si>
-    <t>South Carolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Dakota </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tennessee </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texas </t>
-  </si>
-  <si>
-    <t>Utah</t>
-  </si>
-  <si>
-    <t>Vermont</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Washington </t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wyoming </t>
   </si>
   <si>
     <t>subregion52</t>
@@ -1666,15 +1513,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1684,27 +1531,27 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -1714,78 +1561,78 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="5" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="5" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23" s="5" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="5" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25" s="5" t="s">
-        <v>172</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.35">
@@ -1795,12 +1642,12 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31" s="5" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.35">
@@ -1808,12 +1655,12 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.35">
@@ -1823,12 +1670,12 @@
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="5" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.35">
@@ -1836,12 +1683,12 @@
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" s="3" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.35">
@@ -1851,12 +1698,12 @@
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" s="5" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.35">
@@ -1864,12 +1711,12 @@
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" s="3" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.35">
@@ -1879,12 +1726,12 @@
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>185</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B49" s="5" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -1897,98 +1744,98 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="B62" s="7"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>156</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>157</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>159</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>160</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2015,7 +1862,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -2025,19 +1872,19 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2047,11 +1894,11 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -2059,68 +1906,68 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="F7" s="17"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F8" s="17"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="F9" s="17"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" s="18" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
@@ -2128,7 +1975,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="36"/>
@@ -2164,7 +2011,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="B15">
         <v>2020</v>
@@ -2262,7 +2109,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="B16" s="30">
         <f>(B15-2018)/(2025-2018)*(0.22-0.045)+0.045</f>
@@ -2381,7 +2228,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="B17" s="30">
         <f t="shared" ref="B17:G17" si="2">B16</f>
@@ -2500,7 +2347,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="B18" s="30">
         <v>0</v>
@@ -2613,7 +2460,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" s="16" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="B19" s="30">
         <v>0</v>
@@ -2726,7 +2573,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="18" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="B20" s="31">
         <v>0</v>
@@ -2839,7 +2686,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -2855,7 +2702,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" s="29" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="L23" s="16"/>
     </row>
@@ -2895,7 +2742,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="16" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>5163.6589999999997</v>
@@ -2931,7 +2778,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" s="16" t="s">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="B26">
         <v>1811.1769999999999</v>
@@ -2967,7 +2814,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" s="32" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="B27" s="26">
         <f t="shared" ref="B27:K27" si="4">B26*400/AVERAGE($B26:$D26)</f>
@@ -3013,7 +2860,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" s="16" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="B28">
         <v>223.32400000000001</v>
@@ -3049,7 +2896,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" s="16" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="B29">
         <v>9.4309999999999992</v>
@@ -3085,7 +2932,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" s="16" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="B30">
         <v>54.898000000000003</v>
@@ -3121,7 +2968,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="B31">
         <v>39.978000000000002</v>
@@ -3157,7 +3004,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="B32">
         <v>46.853999999999999</v>
@@ -3193,7 +3040,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="16" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="B33">
         <v>194.715</v>
@@ -3226,12 +3073,12 @@
         <v>221.88900000000001</v>
       </c>
       <c r="L33" s="34" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="32" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="B34" s="26">
         <f t="shared" ref="B34:K34" si="5">SUM(B28,B29:B31,B32:B33)*$L50/SUM($L50:$L51)</f>
@@ -3280,7 +3127,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="32" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="B35" s="26">
         <f t="shared" ref="B35:K35" si="6">SUM(B32:B33)-B34</f>
@@ -3340,12 +3187,12 @@
       <c r="J36" s="26"/>
       <c r="K36" s="26"/>
       <c r="L36" s="34" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="16" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="B37">
         <f>SUM(B27:B28)</f>
@@ -3394,7 +3241,7 @@
     </row>
     <row r="38" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="16" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="B38">
         <f t="shared" ref="B38:K38" si="8">SUM(B29:B31)</f>
@@ -3443,7 +3290,7 @@
     </row>
     <row r="39" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="16" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="B39">
         <f>SUM(B27:B31)</f>
@@ -3489,7 +3336,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="16" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="B40">
         <f>SUM(B32:B33)</f>
@@ -3535,7 +3382,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="18" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="B41" s="19">
         <f>SUM(B28:B33,B25:B26)</f>
@@ -3581,17 +3428,17 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="27" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="28" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -3606,7 +3453,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="K46" s="17"/>
     </row>
@@ -3645,7 +3492,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="B48">
         <v>2452000</v>
@@ -3680,7 +3527,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="B49">
         <v>7819000</v>
@@ -3713,13 +3560,13 @@
         <v>10500105</v>
       </c>
       <c r="L49" s="13" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="M49" s="15"/>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" s="16" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="C50">
         <f>C48-B48</f>
@@ -3765,7 +3612,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" s="18" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="19">
@@ -3812,7 +3659,7 @@
     </row>
     <row r="53" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="B53" s="36"/>
       <c r="C53" s="36"/>
@@ -3820,13 +3667,13 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="D54" s="17"/>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" s="47" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="B55" s="48"/>
       <c r="C55" s="49"/>
@@ -3840,35 +3687,35 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" s="42" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="D57" s="17"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" s="42" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="D58" s="17"/>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" s="42"/>
       <c r="B59" s="9" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="D59" s="17"/>
     </row>
@@ -3892,12 +3739,12 @@
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="B64">
         <v>2020</v>
@@ -3995,7 +3842,7 @@
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="B65" s="12">
         <f>B16</f>
@@ -4124,7 +3971,7 @@
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="B66" s="12">
         <f>B17</f>
@@ -4253,7 +4100,7 @@
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B67" s="12">
         <v>0</v>
@@ -4378,7 +4225,7 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="B68" s="12">
         <v>0</v>
@@ -4476,7 +4323,7 @@
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B69" s="12">
         <v>0</v>
@@ -4601,7 +4448,7 @@
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B70" s="12">
         <v>0</v>
@@ -4726,7 +4573,7 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B71" s="12">
         <v>0</v>
@@ -4944,7 +4791,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="B2" s="12">
         <f>'EPS Vehicle Class Mapping'!B65</f>
@@ -5073,7 +4920,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="B3" s="12">
         <f>'EPS Vehicle Class Mapping'!B66</f>
@@ -5202,7 +5049,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B4" s="12">
         <f>'EPS Vehicle Class Mapping'!B67</f>
@@ -5331,7 +5178,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="B5" s="12">
         <f>'EPS Vehicle Class Mapping'!B68</f>
@@ -5460,7 +5307,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B6" s="12">
         <f>'EPS Vehicle Class Mapping'!B69</f>
@@ -5589,7 +5436,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B7" s="12">
         <f>'EPS Vehicle Class Mapping'!B70</f>
@@ -5718,7 +5565,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B8" s="12">
         <f>'EPS Vehicle Class Mapping'!B71</f>
@@ -5847,43 +5694,43 @@
     </row>
     <row r="11" spans="1:32" ht="29" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="46" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="C11" s="53"/>
       <c r="D11" s="54"/>
       <c r="E11" s="50" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="F11" s="51"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B12" s="29" t="s">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D12" s="45" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="F12" s="45" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>143</v>
       </c>
       <c r="B13" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="16">
         <v>0</v>
@@ -5896,7 +5743,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="B14" s="16">
         <v>0</v>
@@ -5912,7 +5759,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="B15" s="16">
         <v>0</v>
@@ -5928,7 +5775,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>146</v>
       </c>
       <c r="B16" s="16">
         <v>0</v>
@@ -5944,7 +5791,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="B17" s="16">
         <v>1</v>
@@ -5964,7 +5811,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="B18" s="16">
         <v>1</v>
@@ -5982,7 +5829,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="B19" s="16">
         <v>1</v>
@@ -6000,7 +5847,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="B20" s="16">
         <v>0</v>
@@ -6018,7 +5865,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="B21" s="16">
         <v>0</v>
@@ -6034,7 +5881,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="B22" s="16">
         <v>0</v>
@@ -6050,7 +5897,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="B23" s="16">
         <v>0</v>
@@ -6066,7 +5913,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="B24" s="16">
         <v>0</v>
@@ -6082,7 +5929,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="B25" s="16">
         <v>0</v>
@@ -6098,7 +5945,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="B26" s="16">
         <v>0</v>
@@ -6114,7 +5961,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="B27" s="16">
         <v>0</v>
@@ -6130,7 +5977,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="B28" s="16">
         <v>0</v>
@@ -6146,7 +5993,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>159</v>
       </c>
       <c r="B29" s="16">
         <v>0</v>
@@ -6162,7 +6009,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="B30" s="16">
         <v>0</v>
@@ -6178,7 +6025,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="B31" s="16">
         <v>0</v>
@@ -6194,7 +6041,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>162</v>
       </c>
       <c r="B32" s="16">
         <v>1</v>
@@ -6212,7 +6059,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="B33" s="16">
         <v>1</v>
@@ -6230,7 +6077,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>164</v>
       </c>
       <c r="B34" s="16">
         <v>1</v>
@@ -6250,7 +6097,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="B35" s="16">
         <v>0</v>
@@ -6266,7 +6113,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="B36" s="16">
         <v>1</v>
@@ -6284,7 +6131,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="B37" s="16">
         <v>0</v>
@@ -6300,7 +6147,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="B38" s="16">
         <v>0</v>
@@ -6316,7 +6163,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="B39" s="16">
         <v>0</v>
@@ -6332,7 +6179,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="B40" s="16">
         <v>0</v>
@@ -6348,7 +6195,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="B41" s="16">
         <v>1</v>
@@ -6366,7 +6213,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="B42" s="16">
         <v>0</v>
@@ -6382,7 +6229,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="B43" s="16">
         <v>1</v>
@@ -6402,7 +6249,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="B44" s="16">
         <v>1</v>
@@ -6420,7 +6267,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="B45" s="16">
         <v>1</v>
@@ -6440,7 +6287,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="B46" s="16">
         <v>0</v>
@@ -6456,7 +6303,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="B47" s="16">
         <v>0</v>
@@ -6472,7 +6319,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="B48" s="16">
         <v>0</v>
@@ -6488,7 +6335,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="B49" s="16">
         <v>0</v>
@@ -6504,7 +6351,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="B50" s="16">
         <v>1</v>
@@ -6524,7 +6371,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="B51" s="16">
         <v>0</v>
@@ -6540,7 +6387,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="B52" s="16">
         <v>1</v>
@@ -6558,7 +6405,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="B53" s="16">
         <v>0</v>
@@ -6574,7 +6421,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="B54" s="16">
         <v>0</v>
@@ -6590,7 +6437,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="B55" s="16">
         <v>0</v>
@@ -6606,7 +6453,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="B56" s="16">
         <v>0</v>
@@ -6622,7 +6469,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="B57" s="16">
         <v>0</v>
@@ -6638,7 +6485,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="B58" s="16">
         <v>1</v>
@@ -6656,7 +6503,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>189</v>
       </c>
       <c r="B59" s="16">
         <v>1</v>
@@ -6674,7 +6521,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="B60" s="16">
         <v>1</v>
@@ -6694,7 +6541,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="B61" s="16">
         <v>0</v>
@@ -6710,7 +6557,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="B62" s="16">
         <v>0</v>
@@ -6726,7 +6573,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="B63" s="16">
         <v>0</v>
@@ -6742,7 +6589,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B64" s="16">
         <v>0</v>
@@ -6758,7 +6605,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B65" s="16">
         <v>0</v>
@@ -6774,7 +6621,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B66" s="16">
         <v>0</v>
@@ -6790,7 +6637,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B67" s="16">
         <v>0</v>
@@ -6806,7 +6653,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B68" s="16">
         <v>0</v>
@@ -6822,7 +6669,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B69" s="16">
         <v>0</v>
@@ -6838,7 +6685,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B70" s="16">
         <v>0</v>
@@ -6854,7 +6701,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B71" s="16">
         <v>0</v>
@@ -6870,7 +6717,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B72" s="18">
         <v>0</v>
@@ -6907,7 +6754,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -7005,105 +6852,136 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=B$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!B$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!B$2),0)</f>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=C$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!C$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!C$2),0)</f>
+        <v>0.12</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=D$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!D$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!D$2),0)</f>
+        <v>0.14499999999999999</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=E$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!E$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!E$2),0)</f>
+        <v>0.16999999999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=F$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!F$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!F$2),0)</f>
+        <v>0.19500000000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=G$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!G$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!G$2),0)</f>
+        <v>0.21999999999999997</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=H$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!H$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!H$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=I$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!I$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!I$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=J$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!J$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!J$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=K$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!K$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!K$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=L$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!L$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!L$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=M$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!M$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!M$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=N$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!N$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!N$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=O$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!O$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!O$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=P$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!P$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!P$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=Q$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!Q$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!Q$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=R$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!R$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!R$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=S$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!S$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!S$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=T$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!T$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!T$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=U$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!U$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!U$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=V$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!V$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!V$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=W$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!W$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!W$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=X$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!X$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!X$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=Y$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!Y$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!Y$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=Z$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!Z$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!Z$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=AA$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!AA$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!AA$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=AB$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!AB$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!AB$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=AC$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!AC$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!AC$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=AD$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!AD$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!AD$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=AE$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!AE$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!AE$2),0)</f>
+        <v>0.22</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <f>IF(INDEX('CA Standards and Followers'!$E$13:$E$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))&lt;=AF$1,IF(INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))=1,'CA Standards and Followers'!AF$3*INDEX('CA Standards and Followers'!$C$13:$C$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0)),INDEX('CA Standards and Followers'!$B$13:$B$72,MATCH($A2,'CA Standards and Followers'!$A$13:$A$72,0))*'CA Standards and Followers'!AF$2),0)</f>
+        <v>0.22</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7201,7 +7079,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7299,7 +7177,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -7397,7 +7275,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7495,7 +7373,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7593,7 +7471,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7691,7 +7569,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7789,7 +7667,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -7887,7 +7765,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -7985,7 +7863,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -8083,7 +7961,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -8181,7 +8059,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -8279,7 +8157,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -8377,7 +8255,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -8475,7 +8353,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -8573,7 +8451,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -8671,7 +8549,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -8769,7 +8647,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -8867,7 +8745,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -8965,7 +8843,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -9063,7 +8941,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -9161,7 +9039,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -9259,7 +9137,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -9357,7 +9235,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -9455,7 +9333,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -9553,7 +9431,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -9651,7 +9529,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -9749,7 +9627,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -9847,7 +9725,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -9945,7 +9823,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -10043,7 +9921,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -10141,7 +10019,7 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -10239,7 +10117,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -10337,7 +10215,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -10435,7 +10313,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -10533,7 +10411,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -10631,7 +10509,7 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -10729,7 +10607,7 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -10827,7 +10705,7 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -10925,7 +10803,7 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -11023,7 +10901,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -11121,7 +10999,7 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -11219,7 +11097,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -11317,7 +11195,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -11415,7 +11293,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -11513,7 +11391,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -11611,7 +11489,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -11709,7 +11587,7 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -11807,7 +11685,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -11905,7 +11783,7 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -12003,7 +11881,7 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -12101,7 +11979,7 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -12199,7 +12077,7 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -12297,7 +12175,7 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -12395,7 +12273,7 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -12493,7 +12371,7 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -12591,7 +12469,7 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -12689,7 +12567,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -12787,7 +12665,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -12901,7 +12779,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -12999,7 +12877,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -13097,7 +12975,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -13195,7 +13073,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -13293,7 +13171,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -13391,7 +13269,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -13489,7 +13367,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -13587,7 +13465,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -13685,7 +13563,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -13783,7 +13661,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -13881,7 +13759,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -13979,7 +13857,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -14077,7 +13955,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -14175,7 +14053,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -14273,7 +14151,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -14371,7 +14249,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -14469,7 +14347,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -14567,7 +14445,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -14665,7 +14543,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -14763,7 +14641,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -14861,7 +14739,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -14959,7 +14837,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -15057,7 +14935,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -15155,7 +15033,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -15253,7 +15131,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -15351,7 +15229,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -15449,7 +15327,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -15547,7 +15425,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -15645,7 +15523,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -15743,7 +15621,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -15841,7 +15719,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -15939,7 +15817,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -16037,7 +15915,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -16135,7 +16013,7 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -16233,7 +16111,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -16331,7 +16209,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -16429,7 +16307,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -16527,7 +16405,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -16625,7 +16503,7 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -16723,7 +16601,7 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -16821,7 +16699,7 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -16919,7 +16797,7 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -17017,7 +16895,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -17115,7 +16993,7 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -17213,7 +17091,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -17311,7 +17189,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -17409,7 +17287,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -17507,7 +17385,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -17605,7 +17483,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -17703,7 +17581,7 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -17801,7 +17679,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -17899,7 +17777,7 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -17997,7 +17875,7 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -18095,7 +17973,7 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -18193,7 +18071,7 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -18291,7 +18169,7 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -18389,7 +18267,7 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -18487,7 +18365,7 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -18585,7 +18463,7 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -18683,7 +18561,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -18781,7 +18659,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -18895,7 +18773,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -18993,7 +18871,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -19091,7 +18969,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -19189,7 +19067,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -19287,7 +19165,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -19385,7 +19263,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -19483,7 +19361,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -19581,7 +19459,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -19679,7 +19557,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -19777,7 +19655,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -19875,7 +19753,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -19973,7 +19851,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -20071,7 +19949,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -20169,7 +20047,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -20267,7 +20145,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -20365,7 +20243,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -20463,7 +20341,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -20561,7 +20439,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -20659,7 +20537,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -20757,7 +20635,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -20855,7 +20733,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -20953,7 +20831,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -21051,7 +20929,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -21149,7 +21027,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -21247,7 +21125,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -21345,7 +21223,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -21443,7 +21321,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -21541,7 +21419,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -21639,7 +21517,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -21737,7 +21615,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -21835,7 +21713,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -21933,7 +21811,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -22031,7 +21909,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -22129,7 +22007,7 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -22227,7 +22105,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -22325,7 +22203,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -22423,7 +22301,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -22521,7 +22399,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -22619,7 +22497,7 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -22717,7 +22595,7 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -22815,7 +22693,7 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -22913,7 +22791,7 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -23011,7 +22889,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -23109,7 +22987,7 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -23207,7 +23085,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -23305,7 +23183,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -23403,7 +23281,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -23501,7 +23379,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -23599,7 +23477,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -23697,7 +23575,7 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -23795,7 +23673,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -23893,7 +23771,7 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -23991,7 +23869,7 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -24089,7 +23967,7 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -24187,7 +24065,7 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -24285,7 +24163,7 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -24383,7 +24261,7 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -24481,7 +24359,7 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -24579,7 +24457,7 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -24677,7 +24555,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -24775,7 +24653,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -24889,7 +24767,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -24987,7 +24865,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -25085,7 +24963,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -25183,7 +25061,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -25281,7 +25159,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -25379,7 +25257,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -25477,7 +25355,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -25575,7 +25453,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -25673,7 +25551,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -25771,7 +25649,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -25869,7 +25747,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -25967,7 +25845,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -26065,7 +25943,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -26163,7 +26041,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -26261,7 +26139,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -26359,7 +26237,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -26457,7 +26335,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -26555,7 +26433,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -26653,7 +26531,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -26751,7 +26629,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -26849,7 +26727,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -26947,7 +26825,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -27045,7 +26923,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -27143,7 +27021,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -27241,7 +27119,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -27339,7 +27217,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -27437,7 +27315,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -27535,7 +27413,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -27633,7 +27511,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -27731,7 +27609,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -27829,7 +27707,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -27927,7 +27805,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -28025,7 +27903,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -28123,7 +28001,7 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -28221,7 +28099,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -28319,7 +28197,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -28417,7 +28295,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -28515,7 +28393,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -28613,7 +28491,7 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -28711,7 +28589,7 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -28809,7 +28687,7 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -28907,7 +28785,7 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -29005,7 +28883,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -29103,7 +28981,7 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -29201,7 +29079,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -29299,7 +29177,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -29397,7 +29275,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -29495,7 +29373,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -29593,7 +29471,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -29691,7 +29569,7 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -29789,7 +29667,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -29887,7 +29765,7 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -29985,7 +29863,7 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -30083,7 +29961,7 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -30181,7 +30059,7 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -30279,7 +30157,7 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -30377,7 +30255,7 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -30475,7 +30353,7 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -30573,7 +30451,7 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -30671,7 +30549,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -30769,7 +30647,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -30884,7 +30762,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -30982,7 +30860,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -31080,7 +30958,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -31178,7 +31056,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -31276,7 +31154,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -31374,7 +31252,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -31472,7 +31350,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -31570,7 +31448,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -31668,7 +31546,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -31766,7 +31644,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -31864,7 +31742,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -31962,7 +31840,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -32060,7 +31938,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -32158,7 +32036,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -32256,7 +32134,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -32354,7 +32232,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -32452,7 +32330,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -32550,7 +32428,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -32648,7 +32526,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -32746,7 +32624,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -32844,7 +32722,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -32942,7 +32820,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -33040,7 +32918,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -33138,7 +33016,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -33236,7 +33114,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -33334,7 +33212,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -33432,7 +33310,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -33530,7 +33408,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -33628,7 +33506,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -33726,7 +33604,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -33824,7 +33702,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -33922,7 +33800,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -34020,7 +33898,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -34118,7 +33996,7 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -34216,7 +34094,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -34314,7 +34192,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -34412,7 +34290,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -34510,7 +34388,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -34608,7 +34486,7 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -34706,7 +34584,7 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -34804,7 +34682,7 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -34902,7 +34780,7 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -35000,7 +34878,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -35098,7 +34976,7 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -35196,7 +35074,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -35294,7 +35172,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -35392,7 +35270,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -35490,7 +35368,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -35588,7 +35466,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -35686,7 +35564,7 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -35784,7 +35662,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -35882,7 +35760,7 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -35980,7 +35858,7 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -36078,7 +35956,7 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -36176,7 +36054,7 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -36274,7 +36152,7 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -36372,7 +36250,7 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -36470,7 +36348,7 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -36568,7 +36446,7 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -36666,7 +36544,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -36764,7 +36642,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -36878,7 +36756,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -36976,7 +36854,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -37074,7 +36952,7 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -37172,7 +37050,7 @@
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -37270,7 +37148,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -37368,7 +37246,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -37466,7 +37344,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -37564,7 +37442,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -37662,7 +37540,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -37760,7 +37638,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -37858,7 +37736,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -37956,7 +37834,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -38054,7 +37932,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -38152,7 +38030,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -38250,7 +38128,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -38348,7 +38226,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>157</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -38446,7 +38324,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -38544,7 +38422,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -38642,7 +38520,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -38740,7 +38618,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -38838,7 +38716,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>162</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -38936,7 +38814,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>163</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -39034,7 +38912,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -39132,7 +39010,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>216</v>
+        <v>165</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -39230,7 +39108,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -39328,7 +39206,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>167</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -39426,7 +39304,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -39524,7 +39402,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -39622,7 +39500,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -39720,7 +39598,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -39818,7 +39696,7 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -39916,7 +39794,7 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -40014,7 +39892,7 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -40112,7 +39990,7 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -40210,7 +40088,7 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -40308,7 +40186,7 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -40406,7 +40284,7 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -40504,7 +40382,7 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>230</v>
+        <v>179</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -40602,7 +40480,7 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -40700,7 +40578,7 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>181</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -40798,7 +40676,7 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -40896,7 +40774,7 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -40994,7 +40872,7 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>184</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -41092,7 +40970,7 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -41190,7 +41068,7 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -41288,7 +41166,7 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -41386,7 +41264,7 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -41484,7 +41362,7 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -41582,7 +41460,7 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -41680,7 +41558,7 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -41778,7 +41656,7 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>243</v>
+        <v>192</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -41876,7 +41754,7 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>193</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -41974,7 +41852,7 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -42072,7 +41950,7 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -42170,7 +42048,7 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -42268,7 +42146,7 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -42366,7 +42244,7 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -42464,7 +42342,7 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -42562,7 +42440,7 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -42660,7 +42538,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -42758,7 +42636,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B61">
         <v>0</v>
